--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R6a05e973a5bb43a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="Rb1c8c7224db748d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -52,11 +52,17 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
+      <x:color rgb="FF86591B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:color rgb="FF21633C"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -75,6 +81,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE5F2E9"/>
       </x:patternFill>
     </x:fill>
@@ -85,7 +96,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -127,6 +138,12 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -175,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H16"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -410,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-09-30 17:14:21（北京时间）</x:v>
+        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -447,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,A5)</x:f>
-        <x:v>7</x:v>
+        <x:f>COUNTIF(C8:C16,A5)</x:f>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,D5)</x:f>
+        <x:f>COUNTIF(C8:C16,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C14,F5)</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIF(C8:C16,F5)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -503,197 +520,221 @@
         <x:v>用户备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="92" customHeight="1">
+    <x:row r="8" ht="75" customHeight="1">
       <x:c r="A8" s="7" t="str">
+        <x:v>CA-036.03</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="str">
+        <x:v>White 原贴图漏烘焙黑点</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D8" s="7" t="str">
+        <x:v>最新修复聊天确认少量黑点来自原贴图漏烘焙像素，最终交付明确仍保留。衣服形体、权重及重复内层修复不包含这些贴图像素。</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="str">
+        <x:v>确认是否接受少量黑点或另行授权贴图修复；现有交付不能声称黑点已消除。</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="G8" s="7" t="str">
+        <x:v>White 衣服修复聊天最终说明：少量原贴图黑点保留</x:v>
+      </x:c>
+      <x:c r="H8" s="16" t="str"/>
+    </x:row>
+    <x:row r="9" ht="92" customHeight="1">
+      <x:c r="A9" s="7" t="str">
         <x:v>CA-001.04</x:v>
       </x:c>
-      <x:c r="B8" s="7" t="str">
+      <x:c r="B9" s="7" t="str">
         <x:v>White 新校服材质、校徽与裤侧白条</x:v>
       </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D8" s="7" t="str">
+      <x:c r="C9" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="str">
         <x:v>UE 新衣裤已绑定 M_White_SchoolUniform、M_White_SchoolPants，校徽与裤侧白条保留；最终效果图已交付。运行验证确认全部 30 人使用新服装材质。</x:v>
       </x:c>
-      <x:c r="E8" s="7" t="str">
+      <x:c r="E9" s="7" t="str">
         <x:v>本项已验收；最新 White 外观按 9 月 30 日结果追踪。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
+      <x:c r="F9" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="G8" s="7" t="str">
+      <x:c r="G9" s="7" t="str">
         <x:v>新服装材质导入与最终效果交付</x:v>
       </x:c>
-      <x:c r="H8" s="16" t="str"/>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
-      <x:c r="A9" s="7" t="str">
+      <x:c r="H9" s="16" t="str"/>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="7" t="str">
         <x:v>CA-006</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>男学生面部与身体肤色统一</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="str">
+      <x:c r="C10" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="str">
         <x:v>脸、颈、手臂和手掌基色已统一，修复后的贴图与完整角色已导出并接入 UE。</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="str">
+      <x:c r="E10" s="7" t="str">
         <x:v>后续基色或光照修改复核脸、颈与手臂的色差。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
+      <x:c r="F10" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="str">
+      <x:c r="G10" s="7" t="str">
         <x:v>男学生修复源说明与导出交叉检查记录</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str"/>
-    </x:row>
-    <x:row r="10" ht="109" customHeight="1">
-      <x:c r="A10" s="7" t="str">
+      <x:c r="H10" s="16" t="str"/>
+    </x:row>
+    <x:row r="11" ht="109" customHeight="1">
+      <x:c r="A11" s="7" t="str">
         <x:v>CA-007</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="str">
+      <x:c r="B11" s="7" t="str">
         <x:v>学生上衣和裤子布料着色与织纹</x:v>
       </x:c>
-      <x:c r="C10" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="str">
+      <x:c r="C11" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="str">
         <x:v>5 个服装材质加入 Cloth/Substrate 布料着色、切线微法线、粗糙度变化与纤维反光。上衣 roughness 0.82、裤子 0.77，织纹周期约 1.5 mm，远处织纹按屏幕导数衰减；三类角色近景检查完成。</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="str">
+      <x:c r="E11" s="7" t="str">
         <x:v>9 月 29 日材质验收有效；White 最新衣裤材质以 CA-001 的 9 月 30 日换装结果为准。</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46294</x:v>
-      </x:c>
-      <x:c r="G10" s="7" t="str">
-        <x:v>学生布料参数、远处织纹与近景验收</x:v>
-      </x:c>
-      <x:c r="H10" s="16" t="str"/>
-    </x:row>
-    <x:row r="11" ht="92" customHeight="1">
-      <x:c r="A11" s="7" t="str">
-        <x:v>CA-007.02</x:v>
-      </x:c>
-      <x:c r="B11" s="7" t="str">
-        <x:v>男学生合并图集衣物遮罩与混色防护</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="str">
-        <x:v>4096 遮罩用 R 区分上衣、G 区分裤子，非衣物保留原自发光外观。原基色和遮罩设置常驻并从最高精度 mip 取样，防止细小 UV 岛低清混色，源像素未变。</x:v>
-      </x:c>
-      <x:c r="E11" s="7" t="str">
-        <x:v>本次图集保护已实现；后续图集或 UV 改动需更新遮罩。常驻纹理带来的内存增加按现有记录保留。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="n">
         <x:v>46294</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
+        <x:v>学生布料参数、远处织纹与近景验收</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="str"/>
+    </x:row>
+    <x:row r="12" ht="92" customHeight="1">
+      <x:c r="A12" s="7" t="str">
+        <x:v>CA-007.02</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="str">
+        <x:v>男学生合并图集衣物遮罩与混色防护</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
+        <x:v>4096 遮罩用 R 区分上衣、G 区分裤子，非衣物保留原自发光外观。原基色和遮罩设置常驻并从最高精度 mip 取样，防止细小 UV 岛低清混色，源像素未变。</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="str">
+        <x:v>本次图集保护已实现；后续图集或 UV 改动需更新遮罩。常驻纹理带来的内存增加按现有记录保留。</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="n">
+        <x:v>46294</x:v>
+      </x:c>
+      <x:c r="G12" s="7" t="str">
         <x:v>男学生织物遮罩与图集采样设置</x:v>
       </x:c>
-      <x:c r="H11" s="16" t="str"/>
-    </x:row>
-    <x:row r="12" ht="75" customHeight="1">
-      <x:c r="A12" s="7" t="str">
+      <x:c r="H12" s="16" t="str"/>
+    </x:row>
+    <x:row r="13" ht="75" customHeight="1">
+      <x:c r="A13" s="7" t="str">
         <x:v>CA-017.02</x:v>
       </x:c>
-      <x:c r="B12" s="7" t="str">
+      <x:c r="B13" s="7" t="str">
         <x:v>教学楼 B 真正运行画面发黑消除</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D12" s="7" t="str">
+      <x:c r="C13" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
         <x:v>真实 PIE 固定相机回切旧批次与修正批次，发黑随旧变换恢复、修正后消失；668 批次、5,534 实例修复，建筑材质和布局保留。</x:v>
       </x:c>
-      <x:c r="E12" s="7" t="str">
+      <x:c r="E13" s="7" t="str">
         <x:v>教学楼 B 修改后复查真实游戏画面及墙面、走廊显示。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
+      <x:c r="F13" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G12" s="7" t="str">
+      <x:c r="G13" s="7" t="str">
         <x:v>教学楼 B 修复记录：真实 PIE 回切验证</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="str"/>
-    </x:row>
-    <x:row r="13" ht="92" customHeight="1">
-      <x:c r="A13" s="7" t="str">
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="92" customHeight="1">
+      <x:c r="A14" s="7" t="str">
         <x:v>CA-021.03</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="str">
+      <x:c r="B14" s="7" t="str">
         <x:v>校医室材质与独立视觉检查</x:v>
       </x:c>
-      <x:c r="C13" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="str">
+      <x:c r="C14" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
         <x:v>16 种建筑材质、19 种配套材质补齐颜色/粗糙度/金属度，玻璃和候诊棚顶设透明。独立视觉检查未见明显穿插、浮空、树木穿屋、文字镜像或关键设施遗漏。</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="str">
+      <x:c r="E14" s="7" t="str">
         <x:v>本项视觉通过不覆盖真实角色通行；相关运行验收依后续证据更新。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>46288</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="str">
+      <x:c r="G14" s="7" t="str">
         <x:v>校医室材质与视觉完成记录</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str"/>
-    </x:row>
-    <x:row r="14" ht="109" customHeight="1">
-      <x:c r="A14" s="7" t="str">
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="109" customHeight="1">
+      <x:c r="A15" s="7" t="str">
         <x:v>CA-031</x:v>
       </x:c>
-      <x:c r="B14" s="7" t="str">
+      <x:c r="B15" s="7" t="str">
         <x:v>Purple 面部卡通着色与正侧面验收</x:v>
       </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
+      <x:c r="C15" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
         <x:v>面部问题定位为 DefaultLit 高光和阴影造成的分面观感；源几何、UV、拓扑匹配且贴图 alpha 全不透明。面部已改为 Unlit，贴图 RGB 乘亮度 1.65，正面和侧面检查通过，材质已保存且不脏。</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="str">
+      <x:c r="E15" s="7" t="str">
         <x:v>后续面部外观修改以同一正侧面检查为准；身体与颈部保留现有材质。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
+      <x:c r="F15" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G14" s="7" t="str">
+      <x:c r="G15" s="7" t="str">
         <x:v>Purple 面部问题定位、着色修复与保存检查</x:v>
       </x:c>
-      <x:c r="H14" s="16" t="str"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
-      <x:c r="A16" s="3" t="str">
-        <x:v>记录范围</x:v>
-      </x:c>
-      <x:c r="B16" s="19" t="str">
-        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
-      </x:c>
-      <x:c r="C16" s="19"/>
-      <x:c r="D16" s="19"/>
-      <x:c r="E16" s="19"/>
-      <x:c r="F16" s="19"/>
-      <x:c r="G16" s="19"/>
-      <x:c r="H16" s="19"/>
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="75" customHeight="1">
+      <x:c r="A16" s="7" t="str">
+        <x:v>CA-040.07</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="str">
+        <x:v>综合楼后方草坪材质接入</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>针对草坪表面平整的问题，已换用带纹理的现有草坪材质；最终近景与俯视检查及保存交付有效。</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="str">
+        <x:v>当前覆盖编辑器画面与材质接入，未新增运行时渲染验收依据。</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G16" s="7" t="str">
+        <x:v>景观草坪材质修正进展与最终截图</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="1"/>
@@ -705,11 +746,35 @@
       <x:c r="G17" s="1"/>
       <x:c r="H17" s="1"/>
     </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="3" t="str">
+        <x:v>记录范围</x:v>
+      </x:c>
+      <x:c r="B18" s="21" t="str">
+        <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
+      </x:c>
+      <x:c r="C18" s="21"/>
+      <x:c r="D18" s="21"/>
+      <x:c r="E18" s="21"/>
+      <x:c r="F18" s="21"/>
+      <x:c r="G18" s="21"/>
+      <x:c r="H18" s="21"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B16:H16"/>
+    <x:mergeCell ref="B18:H18"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C14">
+  <x:conditionalFormatting sqref="C8:C16">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -721,13 +786,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C14">
+    <x:dataValidation type="list" sqref="C8:C16">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf64b14c1252e4a1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5bf1476c354f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="Rb1c8c7224db748d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R68806c32f8c04971"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H21"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-03 09:09:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,23 +464,23 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C16,A5)</x:f>
-        <x:v>8</x:v>
+        <x:f>COUNTIF(C8:C21,A5)</x:f>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C16,D5)</x:f>
+        <x:f>COUNTIF(C8:C21,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C16,F5)</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIF(C8:C21,F5)</x:f>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
     </x:row>
@@ -546,235 +546,355 @@
     </x:row>
     <x:row r="9" ht="92" customHeight="1">
       <x:c r="A9" s="7" t="str">
+        <x:v>CA-049.02</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="str">
+        <x:v>PIE转镜头发糊与TSR拖影诊断</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="D9" s="7" t="str">
+        <x:v>用户在关闭动态模糊后仍指出转镜头有模糊。实际PIE使用TSR，聊天认为可能是时域拖影，但明确尚未通过画面对比确认；默认关闭不能作为观感修复验收。</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="str">
+        <x:v>需要同镜头关闭MotionBlurQuality及临时FXAA对比或其他画面证据，确认原因和是否处理。</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G9" s="7" t="str">
+        <x:v>用户直接反馈与最终诊断限制</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="str"/>
+    </x:row>
+    <x:row r="10" ht="92" customHeight="1">
+      <x:c r="A10" s="7" t="str">
         <x:v>CA-001.04</x:v>
       </x:c>
-      <x:c r="B9" s="7" t="str">
+      <x:c r="B10" s="7" t="str">
         <x:v>White 新校服材质、校徽与裤侧白条</x:v>
       </x:c>
-      <x:c r="C9" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D9" s="7" t="str">
+      <x:c r="C10" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D10" s="7" t="str">
         <x:v>UE 新衣裤已绑定 M_White_SchoolUniform、M_White_SchoolPants，校徽与裤侧白条保留；最终效果图已交付。运行验证确认全部 30 人使用新服装材质。</x:v>
       </x:c>
-      <x:c r="E9" s="7" t="str">
+      <x:c r="E10" s="7" t="str">
         <x:v>本项已验收；最新 White 外观按 9 月 30 日结果追踪。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
+      <x:c r="F10" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="G9" s="7" t="str">
+      <x:c r="G10" s="7" t="str">
         <x:v>新服装材质导入与最终效果交付</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str"/>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="7" t="str">
+      <x:c r="H10" s="16" t="str"/>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11" s="7" t="str">
         <x:v>CA-006</x:v>
       </x:c>
-      <x:c r="B10" s="7" t="str">
+      <x:c r="B11" s="7" t="str">
         <x:v>男学生面部与身体肤色统一</x:v>
       </x:c>
-      <x:c r="C10" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D10" s="7" t="str">
+      <x:c r="C11" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D11" s="7" t="str">
         <x:v>脸、颈、手臂和手掌基色已统一，修复后的贴图与完整角色已导出并接入 UE。</x:v>
       </x:c>
-      <x:c r="E10" s="7" t="str">
+      <x:c r="E11" s="7" t="str">
         <x:v>后续基色或光照修改复核脸、颈与手臂的色差。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
+      <x:c r="F11" s="14" t="n">
         <x:v>46293</x:v>
       </x:c>
-      <x:c r="G10" s="7" t="str">
+      <x:c r="G11" s="7" t="str">
         <x:v>男学生修复源说明与导出交叉检查记录</x:v>
       </x:c>
-      <x:c r="H10" s="16" t="str"/>
-    </x:row>
-    <x:row r="11" ht="109" customHeight="1">
-      <x:c r="A11" s="7" t="str">
+      <x:c r="H11" s="16" t="str"/>
+    </x:row>
+    <x:row r="12" ht="109" customHeight="1">
+      <x:c r="A12" s="7" t="str">
         <x:v>CA-007</x:v>
       </x:c>
-      <x:c r="B11" s="7" t="str">
+      <x:c r="B12" s="7" t="str">
         <x:v>学生上衣和裤子布料着色与织纹</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D11" s="7" t="str">
+      <x:c r="C12" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D12" s="7" t="str">
         <x:v>5 个服装材质加入 Cloth/Substrate 布料着色、切线微法线、粗糙度变化与纤维反光。上衣 roughness 0.82、裤子 0.77，织纹周期约 1.5 mm，远处织纹按屏幕导数衰减；三类角色近景检查完成。</x:v>
       </x:c>
-      <x:c r="E11" s="7" t="str">
+      <x:c r="E12" s="7" t="str">
         <x:v>9 月 29 日材质验收有效；White 最新衣裤材质以 CA-001 的 9 月 30 日换装结果为准。</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46294</x:v>
-      </x:c>
-      <x:c r="G11" s="7" t="str">
-        <x:v>学生布料参数、远处织纹与近景验收</x:v>
-      </x:c>
-      <x:c r="H11" s="16" t="str"/>
-    </x:row>
-    <x:row r="12" ht="92" customHeight="1">
-      <x:c r="A12" s="7" t="str">
-        <x:v>CA-007.02</x:v>
-      </x:c>
-      <x:c r="B12" s="7" t="str">
-        <x:v>男学生合并图集衣物遮罩与混色防护</x:v>
-      </x:c>
-      <x:c r="C12" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D12" s="7" t="str">
-        <x:v>4096 遮罩用 R 区分上衣、G 区分裤子，非衣物保留原自发光外观。原基色和遮罩设置常驻并从最高精度 mip 取样，防止细小 UV 岛低清混色，源像素未变。</x:v>
-      </x:c>
-      <x:c r="E12" s="7" t="str">
-        <x:v>本次图集保护已实现；后续图集或 UV 改动需更新遮罩。常驻纹理带来的内存增加按现有记录保留。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="n">
         <x:v>46294</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
+        <x:v>学生布料参数、远处织纹与近景验收</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="str"/>
+    </x:row>
+    <x:row r="13" ht="92" customHeight="1">
+      <x:c r="A13" s="7" t="str">
+        <x:v>CA-007.02</x:v>
+      </x:c>
+      <x:c r="B13" s="7" t="str">
+        <x:v>男学生合并图集衣物遮罩与混色防护</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D13" s="7" t="str">
+        <x:v>4096 遮罩用 R 区分上衣、G 区分裤子，非衣物保留原自发光外观。原基色和遮罩设置常驻并从最高精度 mip 取样，防止细小 UV 岛低清混色，源像素未变。</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="str">
+        <x:v>本次图集保护已实现；后续图集或 UV 改动需更新遮罩。常驻纹理带来的内存增加按现有记录保留。</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="n">
+        <x:v>46294</x:v>
+      </x:c>
+      <x:c r="G13" s="7" t="str">
         <x:v>男学生织物遮罩与图集采样设置</x:v>
       </x:c>
-      <x:c r="H12" s="16" t="str"/>
-    </x:row>
-    <x:row r="13" ht="75" customHeight="1">
-      <x:c r="A13" s="7" t="str">
+      <x:c r="H13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14" ht="75" customHeight="1">
+      <x:c r="A14" s="7" t="str">
         <x:v>CA-017.02</x:v>
       </x:c>
-      <x:c r="B13" s="7" t="str">
+      <x:c r="B14" s="7" t="str">
         <x:v>教学楼 B 真正运行画面发黑消除</x:v>
       </x:c>
-      <x:c r="C13" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D13" s="7" t="str">
+      <x:c r="C14" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D14" s="7" t="str">
         <x:v>真实 PIE 固定相机回切旧批次与修正批次，发黑随旧变换恢复、修正后消失；668 批次、5,534 实例修复，建筑材质和布局保留。</x:v>
       </x:c>
-      <x:c r="E13" s="7" t="str">
+      <x:c r="E14" s="7" t="str">
         <x:v>教学楼 B 修改后复查真实游戏画面及墙面、走廊显示。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
+      <x:c r="F14" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G13" s="7" t="str">
+      <x:c r="G14" s="7" t="str">
         <x:v>教学楼 B 修复记录：真实 PIE 回切验证</x:v>
       </x:c>
-      <x:c r="H13" s="16" t="str"/>
-    </x:row>
-    <x:row r="14" ht="92" customHeight="1">
-      <x:c r="A14" s="7" t="str">
+      <x:c r="H14" s="16" t="str"/>
+    </x:row>
+    <x:row r="15" ht="92" customHeight="1">
+      <x:c r="A15" s="7" t="str">
         <x:v>CA-021.03</x:v>
       </x:c>
-      <x:c r="B14" s="7" t="str">
+      <x:c r="B15" s="7" t="str">
         <x:v>校医室材质与独立视觉检查</x:v>
       </x:c>
-      <x:c r="C14" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D14" s="7" t="str">
+      <x:c r="C15" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D15" s="7" t="str">
         <x:v>16 种建筑材质、19 种配套材质补齐颜色/粗糙度/金属度，玻璃和候诊棚顶设透明。独立视觉检查未见明显穿插、浮空、树木穿屋、文字镜像或关键设施遗漏。</x:v>
       </x:c>
-      <x:c r="E14" s="7" t="str">
+      <x:c r="E15" s="7" t="str">
         <x:v>本项视觉通过不覆盖真实角色通行；相关运行验收依后续证据更新。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
+      <x:c r="F15" s="14" t="n">
         <x:v>46288</x:v>
       </x:c>
-      <x:c r="G14" s="7" t="str">
+      <x:c r="G15" s="7" t="str">
         <x:v>校医室材质与视觉完成记录</x:v>
       </x:c>
-      <x:c r="H14" s="16" t="str"/>
-    </x:row>
-    <x:row r="15" ht="109" customHeight="1">
-      <x:c r="A15" s="7" t="str">
+      <x:c r="H15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="109" customHeight="1">
+      <x:c r="A16" s="7" t="str">
         <x:v>CA-031</x:v>
       </x:c>
-      <x:c r="B15" s="7" t="str">
+      <x:c r="B16" s="7" t="str">
         <x:v>Purple 面部卡通着色与正侧面验收</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D15" s="7" t="str">
+      <x:c r="C16" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
         <x:v>面部问题定位为 DefaultLit 高光和阴影造成的分面观感；源几何、UV、拓扑匹配且贴图 alpha 全不透明。面部已改为 Unlit，贴图 RGB 乘亮度 1.65，正面和侧面检查通过，材质已保存且不脏。</x:v>
       </x:c>
-      <x:c r="E15" s="7" t="str">
+      <x:c r="E16" s="7" t="str">
         <x:v>后续面部外观修改以同一正侧面检查为准；身体与颈部保留现有材质。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
+      <x:c r="F16" s="14" t="n">
         <x:v>46291</x:v>
       </x:c>
-      <x:c r="G15" s="7" t="str">
+      <x:c r="G16" s="7" t="str">
         <x:v>Purple 面部问题定位、着色修复与保存检查</x:v>
       </x:c>
-      <x:c r="H15" s="16" t="str"/>
-    </x:row>
-    <x:row r="16" ht="75" customHeight="1">
-      <x:c r="A16" s="7" t="str">
+      <x:c r="H16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="75" customHeight="1">
+      <x:c r="A17" s="7" t="str">
         <x:v>CA-040.07</x:v>
       </x:c>
-      <x:c r="B16" s="7" t="str">
+      <x:c r="B17" s="7" t="str">
         <x:v>综合楼后方草坪材质接入</x:v>
       </x:c>
-      <x:c r="C16" s="20" t="str">
-        <x:v>已完成</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="str">
+      <x:c r="C17" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
         <x:v>针对草坪表面平整的问题，已换用带纹理的现有草坪材质；最终近景与俯视检查及保存交付有效。</x:v>
       </x:c>
-      <x:c r="E16" s="7" t="str">
+      <x:c r="E17" s="7" t="str">
         <x:v>当前覆盖编辑器画面与材质接入，未新增运行时渲染验收依据。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
+      <x:c r="F17" s="14" t="n">
         <x:v>46298</x:v>
       </x:c>
-      <x:c r="G16" s="7" t="str">
+      <x:c r="G17" s="7" t="str">
         <x:v>景观草坪材质修正进展与最终截图</x:v>
       </x:c>
-      <x:c r="H16" s="16" t="str"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="1"/>
-      <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
-      <x:c r="H17" s="1"/>
-    </x:row>
-    <x:row r="18" ht="34" customHeight="1">
-      <x:c r="A18" s="3" t="str">
+      <x:c r="H17" s="16" t="str"/>
+    </x:row>
+    <x:row r="18" ht="75" customHeight="1">
+      <x:c r="A18" s="7" t="str">
+        <x:v>CA-043</x:v>
+      </x:c>
+      <x:c r="B18" s="7" t="str">
+        <x:v>校园草花与灌木根部固定风动</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>草花及灌木已接入根部固定、顶部柔摆及细颤；室内盆栽降低风力，地面草坪保持稳定。scene保存后的参数和近景动态检查通过。</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="str">
+        <x:v>通过MPC_CampusWind调整风力；当前范围为校园可见植被。</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G18" s="7" t="str">
+        <x:v>植被风动最终交付与完成说明</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str"/>
+    </x:row>
+    <x:row r="19" ht="75" customHeight="1">
+      <x:c r="A19" s="7" t="str">
+        <x:v>CA-043.02</x:v>
+      </x:c>
+      <x:c r="B19" s="7" t="str">
+        <x:v>校园大树树冠与叶片风动</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>大树树冠慢摆与叶片细颤已保存；树干、椰果等固定材质槽保持稳定，礼堂混合树冠与矮绿篱独立校正。</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="str">
+        <x:v>原网格采用低幅程序风，不能称为逐叶物理模拟。</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G19" s="7" t="str">
+        <x:v>树冠和固定材质槽交付记录</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str"/>
+    </x:row>
+    <x:row r="20" ht="75" customHeight="1">
+      <x:c r="A20" s="7" t="str">
+        <x:v>CA-043.03</x:v>
+      </x:c>
+      <x:c r="B20" s="7" t="str">
+        <x:v>棕榈藤蔓及悬挂花篮固定端风动</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>棕榈按冠心、绿萝按藤根、花篮按篮口处理固定端；容器、金属、土和木材保持固定，花草和棕榈动态预览已交付。</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
+        <x:v>花篮共享木质材质内藤茎保持固定，叶片仅低幅摆动。</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G20" s="7" t="str">
+        <x:v>特殊植被固定端与动态预览交付</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="75" customHeight="1">
+      <x:c r="A21" s="7" t="str">
+        <x:v>CA-049</x:v>
+      </x:c>
+      <x:c r="B21" s="7" t="str">
+        <x:v>项目默认动态模糊关闭</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D21" s="7" t="str">
+        <x:v>DefaultEngine.ini保存r.DefaultFeature.MotionBlur=False；聊天补查实际PIE相机与后期体积均没有重新启用。</x:v>
+      </x:c>
+      <x:c r="E21" s="7" t="str">
+        <x:v>设置已交付；转镜头仍发糊另见CA-049.02。</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="n">
+        <x:v>46298</x:v>
+      </x:c>
+      <x:c r="G21" s="7" t="str">
+        <x:v>配置与PIE补查</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="A23" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B18" s="21" t="str">
+      <x:c r="B23" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C18" s="21"/>
-      <x:c r="D18" s="21"/>
-      <x:c r="E18" s="21"/>
-      <x:c r="F18" s="21"/>
-      <x:c r="G18" s="21"/>
-      <x:c r="H18" s="21"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="1"/>
-      <x:c r="B19" s="1"/>
-      <x:c r="C19" s="1"/>
-      <x:c r="D19" s="1"/>
-      <x:c r="E19" s="1"/>
-      <x:c r="F19" s="1"/>
-      <x:c r="G19" s="1"/>
-      <x:c r="H19" s="1"/>
+      <x:c r="C23" s="21"/>
+      <x:c r="D23" s="21"/>
+      <x:c r="E23" s="21"/>
+      <x:c r="F23" s="21"/>
+      <x:c r="G23" s="21"/>
+      <x:c r="H23" s="21"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B18:H18"/>
+    <x:mergeCell ref="B23:H23"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C16">
+  <x:conditionalFormatting sqref="C8:C21">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -786,13 +906,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C16">
+    <x:dataValidation type="list" sqref="C8:C21">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b5bf1476c354f5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3af27f09d6c40e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R68806c32f8c04971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R73ff1c13e9444a99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H33"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-04 09:15:53（北京时间）</x:v>
+        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,A5)</x:f>
-        <x:v>12</x:v>
+        <x:f>COUNTIF(C8:C33,A5)</x:f>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,D5)</x:f>
+        <x:f>COUNTIF(C8:C33,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C21,F5)</x:f>
+        <x:f>COUNTIF(C8:C33,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -856,45 +856,333 @@
       </x:c>
       <x:c r="H21" s="16" t="str"/>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="1"/>
-      <x:c r="B22" s="1"/>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-    </x:row>
-    <x:row r="23" ht="34" customHeight="1">
-      <x:c r="A23" s="3" t="str">
+    <x:row r="22" ht="75" customHeight="1">
+      <x:c r="A22" s="7" t="str">
+        <x:v>CA-057.03</x:v>
+      </x:c>
+      <x:c r="B22" s="7" t="str">
+        <x:v>长廊自发光灯带接入</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D22" s="7" t="str">
+        <x:v>遵照用户要求，灯带使用自发光材质，两版均未新增UE实际灯光；后续人工灯面已纳入昼夜控制。</x:v>
+      </x:c>
+      <x:c r="E22" s="7" t="str">
+        <x:v>自发光效果的实际渲染成本不由零新增灯光数量推定。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G22" s="7" t="str">
+        <x:v>长廊最终结果与昼夜材质说明</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str"/>
+    </x:row>
+    <x:row r="23" ht="58" customHeight="1">
+      <x:c r="A23" s="7" t="str">
+        <x:v>CA-059.02</x:v>
+      </x:c>
+      <x:c r="B23" s="7" t="str">
+        <x:v>遮荫棕榈宽叶冠风动接入</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D23" s="7" t="str">
+        <x:v>两排棕榈的网格、数量、材质和风动检查通过，最终效果图及保存结果已交付。</x:v>
+      </x:c>
+      <x:c r="E23" s="7" t="str">
+        <x:v>风动整体GPU成本基线仍见CA-043.06。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G23" s="7" t="str">
+        <x:v>palms_verification风动检查</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str"/>
+    </x:row>
+    <x:row r="24" ht="75" customHeight="1">
+      <x:c r="A24" s="7" t="str">
+        <x:v>CA-062</x:v>
+      </x:c>
+      <x:c r="B24" s="7" t="str">
+        <x:v>校园星空月光与固定曝光阶段交付</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D24" s="7" t="str">
+        <x:v>早期夜景黑色星空、月亮和固定曝光已保存；后按参考图改为深蓝薄云夜空。月光基础亮度按用户要求调至2.5lux，该阶段已交付。</x:v>
+      </x:c>
+      <x:c r="E24" s="7" t="str">
+        <x:v>当前天空以CA-063和CA-064的后续结果为准，保留初版阶段记录。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G24" s="7" t="str">
+        <x:v>夜景各轮保存与用户补月光</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str"/>
+    </x:row>
+    <x:row r="25" ht="75" customHeight="1">
+      <x:c r="A25" s="7" t="str">
+        <x:v>CA-062.03</x:v>
+      </x:c>
+      <x:c r="B25" s="7" t="str">
+        <x:v>远景城市冷暖窗灯假光效果</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D25" s="7" t="str">
+        <x:v>19材质变体用于46 Actor/56槽，冷暖交错窗光和地标轮廓光保存；新增实际光源0，原ISM实例数保持。</x:v>
+      </x:c>
+      <x:c r="E25" s="7" t="str">
+        <x:v>后续整体参考氛围以CA-063为准。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G25" s="7" t="str">
+        <x:v>NightSkyline verified</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str"/>
+    </x:row>
+    <x:row r="26" ht="58" customHeight="1">
+      <x:c r="A26" s="7" t="str">
+        <x:v>CA-062.04</x:v>
+      </x:c>
+      <x:c r="B26" s="7" t="str">
+        <x:v>七处地标彩色流动发光</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D26" s="7" t="str">
+        <x:v>7地标、17立面槽接入上行/螺旋/波纹差异光效，原生材质Time驱动并保存。</x:v>
+      </x:c>
+      <x:c r="E26" s="7" t="str">
+        <x:v>材质动效纳入昼夜控制，白天禁灯见CA-064.03。</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G26" s="7" t="str">
+        <x:v>NightLandmarkFX verified</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str"/>
+    </x:row>
+    <x:row r="27" ht="58" customHeight="1">
+      <x:c r="A27" s="7" t="str">
+        <x:v>CA-062.05</x:v>
+      </x:c>
+      <x:c r="B27" s="7" t="str">
+        <x:v>七束地标假射线扫动</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D27" s="7" t="str">
+        <x:v>7束假探照光以材质Time与WPO驱动，不新增真实光源；双帧检查动态变化且scene保存。</x:v>
+      </x:c>
+      <x:c r="E27" s="7" t="str">
+        <x:v>保留原生运行方式，实际渲染性能独立判断。</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G27" s="7" t="str">
+        <x:v>NightLandmarkFX动效与保存</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str"/>
+    </x:row>
+    <x:row r="28" ht="75" customHeight="1">
+      <x:c r="A28" s="7" t="str">
+        <x:v>CA-063</x:v>
+      </x:c>
+      <x:c r="B28" s="7" t="str">
+        <x:v>参考夜景天空曝光薄雾氛围</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D28" s="7" t="str">
+        <x:v>后续设计图版已保存深蓝薄云、稀疏星点、暖地平线、薄雾和固定EV100=2，早期纯黑天空已被当前参考需求修订。</x:v>
+      </x:c>
+      <x:c r="E28" s="7" t="str">
+        <x:v>具体参考细节接受范围另见CA-063.06。</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G28" s="7" t="str">
+        <x:v>NightReference final_verified</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str"/>
+    </x:row>
+    <x:row r="29" ht="58" customHeight="1">
+      <x:c r="A29" s="7" t="str">
+        <x:v>CA-063.03</x:v>
+      </x:c>
+      <x:c r="B29" s="7" t="str">
+        <x:v>远岸六十九假灯点与城市氛围</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D29" s="7" t="str">
+        <x:v>69远岸假灯点及城市暖光氛围完成保存，运行确认far_marker_actors=1且可见激活。</x:v>
+      </x:c>
+      <x:c r="E29" s="7" t="str">
+        <x:v>当前发光随昼夜控制，白天保持关闭。</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G29" s="7" t="str">
+        <x:v>NightReference运行与保存</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str"/>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
+      <x:c r="A30" s="7" t="str">
+        <x:v>CA-063.04</x:v>
+      </x:c>
+      <x:c r="B30" s="7" t="str">
+        <x:v>参考夜景水面反射参数接入</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D30" s="7" t="str">
+        <x:v>水面roughness=0.14、ripple_normal_strength=0.11保存，冷暖水面反射已交付；最终聊天明确碎波仍有差异。</x:v>
+      </x:c>
+      <x:c r="E30" s="7" t="str">
+        <x:v>参数交付与参考效果细节接受分开，见CA-063.06。</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="n">
+        <x:v>46299</x:v>
+      </x:c>
+      <x:c r="G30" s="7" t="str">
+        <x:v>final_verified水面设置</x:v>
+      </x:c>
+      <x:c r="H30" s="16" t="str"/>
+    </x:row>
+    <x:row r="31" ht="92" customHeight="1">
+      <x:c r="A31" s="7" t="str">
+        <x:v>CA-064.03</x:v>
+      </x:c>
+      <x:c r="B31" s="7" t="str">
+        <x:v>灯带窗灯和屏幕昼夜发光接入</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D31" s="7" t="str">
+        <x:v>988材质审计，人工灯面与天空共30母材质接入昼夜控制；新增16建筑母材质保留ISM合批。室内灯、灯带、城市窗灯、屏幕和扫射光白天发光归零。</x:v>
+      </x:c>
+      <x:c r="E31" s="7" t="str">
+        <x:v>材质与真实灯同步，性能未测见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F31" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G31" s="7" t="str">
+        <x:v>emissive_batching与最新使用说明</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str"/>
+    </x:row>
+    <x:row r="32" ht="75" customHeight="1">
+      <x:c r="A32" s="7" t="str">
+        <x:v>CA-064.05</x:v>
+      </x:c>
+      <x:c r="B32" s="7" t="str">
+        <x:v>自然白天天空日照和后期接入</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D32" s="7" t="str">
+        <x:v>按最新参考图完成蓝天柔云、偏中性日照、清晰阴影及独立白天后期层，正午日照8000、EV100=10、补光倍率12，最终预览交付。</x:v>
+      </x:c>
+      <x:c r="E32" s="7" t="str">
+        <x:v>夜间白天后期层权重为零；原夜景保持检查见CA-064.07。</x:v>
+      </x:c>
+      <x:c r="F32" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G32" s="7" t="str">
+        <x:v>白天最终聊天与scene_verified</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str"/>
+    </x:row>
+    <x:row r="33" ht="75" customHeight="1">
+      <x:c r="A33" s="7" t="str">
+        <x:v>CA-064.06</x:v>
+      </x:c>
+      <x:c r="B33" s="7" t="str">
+        <x:v>天空光照色温与云层连续过渡</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D33" s="7" t="str">
+        <x:v>太阳和日轮共轨，日出日落暖色与光照色温平滑变化；云按连续时间漂移，午夜时钟归零不重置位置。</x:v>
+      </x:c>
+      <x:c r="E33" s="7" t="str">
+        <x:v>保持600秒循环与白天禁灯规则。</x:v>
+      </x:c>
+      <x:c r="F33" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G33" s="7" t="str">
+        <x:v>白天最终交付与使用说明</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="34" customHeight="1">
+      <x:c r="A35" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B23" s="21" t="str">
+      <x:c r="B35" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C23" s="21"/>
-      <x:c r="D23" s="21"/>
-      <x:c r="E23" s="21"/>
-      <x:c r="F23" s="21"/>
-      <x:c r="G23" s="21"/>
-      <x:c r="H23" s="21"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="1"/>
-      <x:c r="B24" s="1"/>
-      <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
+      <x:c r="C35" s="21"/>
+      <x:c r="D35" s="21"/>
+      <x:c r="E35" s="21"/>
+      <x:c r="F35" s="21"/>
+      <x:c r="G35" s="21"/>
+      <x:c r="H35" s="21"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B23:H23"/>
+    <x:mergeCell ref="B35:H35"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C21">
+  <x:conditionalFormatting sqref="C8:C33">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -906,13 +1194,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C21">
+    <x:dataValidation type="list" sqref="C8:C33">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3af27f09d6c40e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc568ebd6eee5462e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R73ff1c13e9444a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R1d15a0063aea4074"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H40"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-05 09:12:49（北京时间）</x:v>
+        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -439,7 +439,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>布料、贴图遮罩、人物着色及真实游戏画面。</x:v>
+        <x:v>角色、建筑与环境的材质、贴图、天空光照及渲染效果。</x:v>
       </x:c>
       <x:c r="B3" s="3"/>
       <x:c r="C3" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,A5)</x:f>
-        <x:v>24</x:v>
+        <x:f>COUNTIF(C8:C40,A5)</x:f>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,D5)</x:f>
+        <x:f>COUNTIF(C8:C40,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C33,F5)</x:f>
+        <x:f>COUNTIF(C8:C40,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="H26" s="16" t="str"/>
     </x:row>
-    <x:row r="27" ht="58" customHeight="1">
+    <x:row r="27" ht="92" customHeight="1">
       <x:c r="A27" s="7" t="str">
         <x:v>CA-062.05</x:v>
       </x:c>
@@ -987,16 +987,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D27" s="7" t="str">
-        <x:v>7束假探照光以材质Time与WPO驱动，不新增真实光源；双帧检查动态变化且scene保存。</x:v>
+        <x:v>初版7束假射线慢扫动已交付。新用户要求明显左右往复，现以楼顶为起点平滑扫荡、各束错相位，周期约7.5–12.5秒；7束验证、昼夜连接及8资产保存通过，位置颜色亮度保留。</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>保留原生运行方式，实际渲染性能独立判断。</x:v>
+        <x:v>实际动效和保存通过；低开销预览与显存限制见CA-064.09。</x:v>
       </x:c>
       <x:c r="F27" s="14" t="n">
-        <x:v>46299</x:v>
+        <x:v>46300</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
-        <x:v>NightLandmarkFX动效与保存</x:v>
+        <x:v>最新左右扫荡聊天与保存回读</x:v>
       </x:c>
       <x:c r="H27" s="16" t="str"/>
     </x:row>
@@ -1083,10 +1083,10 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D31" s="7" t="str">
-        <x:v>988材质审计，人工灯面与天空共30母材质接入昼夜控制；新增16建筑母材质保留ISM合批。室内灯、灯带、城市窗灯、屏幕和扫射光白天发光归零。</x:v>
+        <x:v>初版30母材质（含天空）接入记录保留。黄昏修订的29个人工发光材质全部保存并检查通过，灯罩、窗灯、远景和灯带共用提前开灯与曝光过渡。</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
-        <x:v>材质与真实灯同步，性能未测见CA-064.09。</x:v>
+        <x:v>旧白天归零范围仍作为阶段历史；黄昏从17:00提前渐亮。</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
         <x:v>46300</x:v>
@@ -1096,31 +1096,31 @@
       </x:c>
       <x:c r="H31" s="16" t="str"/>
     </x:row>
-    <x:row r="32" ht="75" customHeight="1">
+    <x:row r="32" ht="109" customHeight="1">
       <x:c r="A32" s="7" t="str">
         <x:v>CA-064.05</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
-        <x:v>自然白天天空日照和后期接入</x:v>
+        <x:v>白天独立后期层与昼夜权重接入</x:v>
       </x:c>
       <x:c r="C32" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D32" s="7" t="str">
-        <x:v>按最新参考图完成蓝天柔云、偏中性日照、清晰阴影及独立白天后期层，正午日照8000、EV100=10、补光倍率12，最终预览交付。</x:v>
+        <x:v>独立白天后期层已交付，最新8:00、12:00、17:00权重1，20:00、22:00权重0，回到12:00恢复1。初版8000日照/EV10已被后续正午修订替代，云层与照明修正独立见CA-067、CA-067.02。</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>夜间白天后期层权重为零；原夜景保持检查见CA-064.07。</x:v>
+        <x:v>本项只判断白天后期层接入与权重；黑天空后续修复见CA-067.03。</x:v>
       </x:c>
       <x:c r="F32" s="14" t="n">
         <x:v>46300</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
-        <x:v>白天最终聊天与scene_verified</x:v>
+        <x:v>独立白天后期交付及最新权重回读</x:v>
       </x:c>
       <x:c r="H32" s="16" t="str"/>
     </x:row>
-    <x:row r="33" ht="75" customHeight="1">
+    <x:row r="33" ht="92" customHeight="1">
       <x:c r="A33" s="7" t="str">
         <x:v>CA-064.06</x:v>
       </x:c>
@@ -1131,10 +1131,10 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D33" s="7" t="str">
-        <x:v>太阳和日轮共轨，日出日落暖色与光照色温平滑变化；云按连续时间漂移，午夜时钟归零不重置位置。</x:v>
+        <x:v>太阳与日轮共轨、色温连续变化和云层时间连续性保留。新体积云及天空大气已接入；黄昏曝光随提前开灯同步校正，日落边界连续性16项回归通过。</x:v>
       </x:c>
       <x:c r="E33" s="7" t="str">
-        <x:v>保持600秒循环与白天禁灯规则。</x:v>
+        <x:v>太阳18:00落下；灯具17:00提前渐亮，月亮轨道见CA-068。</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
         <x:v>46300</x:v>
@@ -1144,45 +1144,213 @@
       </x:c>
       <x:c r="H33" s="16" t="str"/>
     </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-    </x:row>
-    <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="3" t="str">
+    <x:row r="34" ht="75" customHeight="1">
+      <x:c r="A34" s="7" t="str">
+        <x:v>CA-064.10</x:v>
+      </x:c>
+      <x:c r="B34" s="7" t="str">
+        <x:v>黄昏灯光曝光与自发光补偿</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D34" s="7" t="str">
+        <x:v>已修正黄昏曝光下灯具与发光面的可见性；29母材质统一提前渐亮，17:45画面交付，夜间原亮度精确恢复。</x:v>
+      </x:c>
+      <x:c r="E34" s="7" t="str">
+        <x:v>灯具启动与达到全亮分开判断；窗口和速度见CA-064.02、CA-064.04。</x:v>
+      </x:c>
+      <x:c r="F34" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G34" s="7" t="str">
+        <x:v>黄昏预览与发光材质回读</x:v>
+      </x:c>
+      <x:c r="H34" s="16" t="str"/>
+    </x:row>
+    <x:row r="35" ht="75" customHeight="1">
+      <x:c r="A35" s="7" t="str">
+        <x:v>CA-067</x:v>
+      </x:c>
+      <x:c r="B35" s="7" t="str">
+        <x:v>平面噪声云替换为体积云</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D35" s="7" t="str">
+        <x:v>用户反馈云不自然后，体积云、天空大气和新云材质已保存；三项昼夜测试及正午画面交付。</x:v>
+      </x:c>
+      <x:c r="E35" s="7" t="str">
+        <x:v>后续日出黑天空修复独立见CA-067.03。</x:v>
+      </x:c>
+      <x:c r="F35" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G35" s="7" t="str">
+        <x:v>正午云层修复交付与场景回读</x:v>
+      </x:c>
+      <x:c r="H35" s="16" t="str"/>
+    </x:row>
+    <x:row r="36" ht="75" customHeight="1">
+      <x:c r="A36" s="7" t="str">
+        <x:v>CA-067.02</x:v>
+      </x:c>
+      <x:c r="B36" s="7" t="str">
+        <x:v>正午Lumen曝光与重复补光修正</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D36" s="7" t="str">
+        <x:v>修复天空光重复放大和Lumen曝光范围，正午日照80000、天空2、EV14；GI与反射均Lumen，减少泛白。</x:v>
+      </x:c>
+      <x:c r="E36" s="7" t="str">
+        <x:v>这是照明参数与观感阶段交付，整体性能另见CA-064.09。</x:v>
+      </x:c>
+      <x:c r="F36" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G36" s="7" t="str">
+        <x:v>正午用户反馈及Lumen设置回读</x:v>
+      </x:c>
+      <x:c r="H36" s="16" t="str"/>
+    </x:row>
+    <x:row r="37" ht="75" customHeight="1">
+      <x:c r="A37" s="7" t="str">
+        <x:v>CA-067.03</x:v>
+      </x:c>
+      <x:c r="B37" s="7" t="str">
+        <x:v>夜转昼天空发黑修复</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D37" s="7" t="str">
+        <x:v>实际PIE确认天空大气和体积云仍被游戏隐藏；修正hidden状态并保存，重载验证通过，第二轮日出和正午画面正常。</x:v>
+      </x:c>
+      <x:c r="E37" s="7" t="str">
+        <x:v>原问题已有新修复依据，不继续固定为未解决。</x:v>
+      </x:c>
+      <x:c r="F37" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G37" s="7" t="str">
+        <x:v>黑天空根因、两轮运行及重载验证</x:v>
+      </x:c>
+      <x:c r="H37" s="16" t="str"/>
+    </x:row>
+    <x:row r="38" ht="75" customHeight="1">
+      <x:c r="A38" s="7" t="str">
+        <x:v>CA-070.02</x:v>
+      </x:c>
+      <x:c r="B38" s="7" t="str">
+        <x:v>教学楼墙地家具金属玻璃真实材质</x:v>
+      </x:c>
+      <x:c r="C38" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D38" s="7" t="str">
+        <x:v>13既有表面材质接共享PBR，墙面抹灰混凝土、地坪水磨石、桌椅木纹及金属细节接入，玻璃参数微调；A/B楼与夜间预览已交付。</x:v>
+      </x:c>
+      <x:c r="E38" s="7" t="str">
+        <x:v>后续门扇按用户改纯色，见CA-070.03；桌椅木纹保留。</x:v>
+      </x:c>
+      <x:c r="F38" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G38" s="7" t="str">
+        <x:v>教学楼真实材质保存与近景交付</x:v>
+      </x:c>
+      <x:c r="H38" s="16" t="str"/>
+    </x:row>
+    <x:row r="39" ht="75" customHeight="1">
+      <x:c r="A39" s="7" t="str">
+        <x:v>CA-070.03</x:v>
+      </x:c>
+      <x:c r="B39" s="7" t="str">
+        <x:v>教学楼门扇门框纯色修订</x:v>
+      </x:c>
+      <x:c r="C39" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D39" s="7" t="str">
+        <x:v>用户要求门无花纹后，门扇暖棕、门框深棕、储物柜白色三材质保存；无纹理节点，918相关组件检查通过，桌椅木纹保留。</x:v>
+      </x:c>
+      <x:c r="E39" s="7" t="str">
+        <x:v>此前木门贴图阶段已被纯色修订替代；开关不受此材质改动影响。</x:v>
+      </x:c>
+      <x:c r="F39" s="14" t="n">
+        <x:v>46300</x:v>
+      </x:c>
+      <x:c r="G39" s="7" t="str">
+        <x:v>用户纯色纠正与918组件验证</x:v>
+      </x:c>
+      <x:c r="H39" s="16" t="str"/>
+    </x:row>
+    <x:row r="40" ht="75" customHeight="1">
+      <x:c r="A40" s="7" t="str">
+        <x:v>CA-071.03</x:v>
+      </x:c>
+      <x:c r="B40" s="7" t="str">
+        <x:v>密铺草叶颜色法线与动态材质接入</x:v>
+      </x:c>
+      <x:c r="C40" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D40" s="7" t="str">
+        <x:v>近景发黑及倒伏已修正：顶点颜色接BaseColor，统一竖直随机yaw，单不透明双面植被材质、WPO风动接入；宿舍庭院路侧画面已交付。</x:v>
+      </x:c>
+      <x:c r="E40" s="7" t="str">
+        <x:v>不把修正前异常保留为当前失败；旋转全量检查见CA-071.05。</x:v>
+      </x:c>
+      <x:c r="F40" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G40" s="7" t="str">
+        <x:v>最新材质与近景检查</x:v>
+      </x:c>
+      <x:c r="H40" s="16" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1"/>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1"/>
+      <x:c r="F41" s="1"/>
+      <x:c r="G41" s="1"/>
+      <x:c r="H41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="34" customHeight="1">
+      <x:c r="A42" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B35" s="21" t="str">
+      <x:c r="B42" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C35" s="21"/>
-      <x:c r="D35" s="21"/>
-      <x:c r="E35" s="21"/>
-      <x:c r="F35" s="21"/>
-      <x:c r="G35" s="21"/>
-      <x:c r="H35" s="21"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="1"/>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
+      <x:c r="C42" s="21"/>
+      <x:c r="D42" s="21"/>
+      <x:c r="E42" s="21"/>
+      <x:c r="F42" s="21"/>
+      <x:c r="G42" s="21"/>
+      <x:c r="H42" s="21"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1"/>
+      <x:c r="D43" s="1"/>
+      <x:c r="E43" s="1"/>
+      <x:c r="F43" s="1"/>
+      <x:c r="G43" s="1"/>
+      <x:c r="H43" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B35:H35"/>
+    <x:mergeCell ref="B42:H42"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C33">
+  <x:conditionalFormatting sqref="C8:C40">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1194,13 +1362,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C33">
+    <x:dataValidation type="list" sqref="C8:C40">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc568ebd6eee5462e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38051f63ac2b4c1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R1d15a0063aea4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R628d6fce17fd48fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H40"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H43"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +427,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-06 09:08:50（北京时间）</x:v>
+        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +464,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C40,A5)</x:f>
-        <x:v>31</x:v>
+        <x:f>COUNTIF(C8:C43,A5)</x:f>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C40,D5)</x:f>
+        <x:f>COUNTIF(C8:C43,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C40,F5)</x:f>
+        <x:f>COUNTIF(C8:C43,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -1312,45 +1312,117 @@
       </x:c>
       <x:c r="H40" s="16" t="str"/>
     </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="1"/>
-      <x:c r="B41" s="1"/>
-      <x:c r="C41" s="1"/>
-      <x:c r="D41" s="1"/>
-      <x:c r="E41" s="1"/>
-      <x:c r="F41" s="1"/>
-      <x:c r="G41" s="1"/>
-      <x:c r="H41" s="1"/>
-    </x:row>
-    <x:row r="42" ht="34" customHeight="1">
-      <x:c r="A42" s="3" t="str">
+    <x:row r="41" ht="92" customHeight="1">
+      <x:c r="A41" s="7" t="str">
+        <x:v>CA-073.03</x:v>
+      </x:c>
+      <x:c r="B41" s="7" t="str">
+        <x:v>室外地面湿润反射与停雨渐干</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D41" s="7" t="str">
+        <x:v>65处室外材质槽接天气副本，保留原贴图和凹凸细节，颜色粗糙度随湿度变化；重载65/65绑定匹配，夜间湿地反射与停雨后渐干通过，100秒后湿度为0。</x:v>
+      </x:c>
+      <x:c r="E41" s="7" t="str">
+        <x:v>只覆盖已绑定室外铺装，不能扩大到所有校园材质。</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G41" s="7" t="str">
+        <x:v>65材质重载与昼夜干湿检查</x:v>
+      </x:c>
+      <x:c r="H41" s="16" t="str"/>
+    </x:row>
+    <x:row r="42" ht="75" customHeight="1">
+      <x:c r="A42" s="7" t="str">
+        <x:v>CA-073.04</x:v>
+      </x:c>
+      <x:c r="B42" s="7" t="str">
+        <x:v>阴雨云层光照及正午曝光修正</x:v>
+      </x:c>
+      <x:c r="C42" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D42" s="7" t="str">
+        <x:v>天气联动体积云、日照、天空光和雾；正午雨景偏暗已修正，天气曝光补偿不累加，昼夜降雨预览通过，夜间白天后期层权重仍为0。</x:v>
+      </x:c>
+      <x:c r="E42" s="7" t="str">
+        <x:v>该项为天气效果接入；基础昼夜与原夜景基准保留阶段依据。</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G42" s="7" t="str">
+        <x:v>最终天气重载及昼夜运行验证</x:v>
+      </x:c>
+      <x:c r="H42" s="16" t="str"/>
+    </x:row>
+    <x:row r="43" ht="75" customHeight="1">
+      <x:c r="A43" s="7" t="str">
+        <x:v>CA-073.05</x:v>
+      </x:c>
+      <x:c r="B43" s="7" t="str">
+        <x:v>加大雨量与雨丝可见度修订</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D43" s="7" t="str">
+        <x:v>用户要求雨改大后，雨丝密度加倍到3600，增强雨丝可见度并略提高下落速度，保存和画面验证通过；后续30秒渐变版本保留该雨量。</x:v>
+      </x:c>
+      <x:c r="E43" s="7" t="str">
+        <x:v>最新雨量按加大版判断，不再沿用初版1800条配置。</x:v>
+      </x:c>
+      <x:c r="F43" s="14" t="n">
+        <x:v>46301</x:v>
+      </x:c>
+      <x:c r="G43" s="7" t="str">
+        <x:v>加大雨量直接纠正与最终预览</x:v>
+      </x:c>
+      <x:c r="H43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1"/>
+      <x:c r="F44" s="1"/>
+      <x:c r="G44" s="1"/>
+      <x:c r="H44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="34" customHeight="1">
+      <x:c r="A45" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B42" s="21" t="str">
+      <x:c r="B45" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C42" s="21"/>
-      <x:c r="D42" s="21"/>
-      <x:c r="E42" s="21"/>
-      <x:c r="F42" s="21"/>
-      <x:c r="G42" s="21"/>
-      <x:c r="H42" s="21"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="1"/>
-      <x:c r="B43" s="1"/>
-      <x:c r="C43" s="1"/>
-      <x:c r="D43" s="1"/>
-      <x:c r="E43" s="1"/>
-      <x:c r="F43" s="1"/>
-      <x:c r="G43" s="1"/>
-      <x:c r="H43" s="1"/>
+      <x:c r="C45" s="21"/>
+      <x:c r="D45" s="21"/>
+      <x:c r="E45" s="21"/>
+      <x:c r="F45" s="21"/>
+      <x:c r="G45" s="21"/>
+      <x:c r="H45" s="21"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1"/>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1"/>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="1"/>
+      <x:c r="H46" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B42:H42"/>
+    <x:mergeCell ref="B45:H45"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C40">
+  <x:conditionalFormatting sqref="C8:C43">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1362,13 +1434,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C40">
+    <x:dataValidation type="list" sqref="C8:C43">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38051f63ac2b4c1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea651e963ac486d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R628d6fce17fd48fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R6facfb6396e645b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,7 +91,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -192,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H43"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H54"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -427,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-07 09:06:54（北京时间）</x:v>
+        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -464,22 +470,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C43,A5)</x:f>
-        <x:v>34</x:v>
+        <x:f>COUNTIF(C8:C54,A5)</x:f>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C43,D5)</x:f>
+        <x:f>COUNTIF(C8:C54,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C43,F5)</x:f>
+        <x:f>COUNTIF(C8:C54,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -536,8 +542,8 @@
       <x:c r="E8" s="7" t="str">
         <x:v>确认是否接受少量黑点或另行授权贴图修复；现有交付不能声称黑点已消除。</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="n">
-        <x:v>46296</x:v>
+      <x:c r="F8" s="14" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G8" s="7" t="str">
         <x:v>White 衣服修复聊天最终说明：少量原贴图黑点保留</x:v>
@@ -560,8 +566,8 @@
       <x:c r="E9" s="7" t="str">
         <x:v>需要同镜头关闭MotionBlurQuality及临时FXAA对比或其他画面证据，确认原因和是否处理。</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F9" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G9" s="7" t="str">
         <x:v>用户直接反馈与最终诊断限制</x:v>
@@ -584,8 +590,8 @@
       <x:c r="E10" s="7" t="str">
         <x:v>本项已验收；最新 White 外观按 9 月 30 日结果追踪。</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="n">
-        <x:v>46295</x:v>
+      <x:c r="F10" s="14" t="d">
+        <x:v>2026-09-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G10" s="7" t="str">
         <x:v>新服装材质导入与最终效果交付</x:v>
@@ -608,8 +614,8 @@
       <x:c r="E11" s="7" t="str">
         <x:v>后续基色或光照修改复核脸、颈与手臂的色差。</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>46293</x:v>
+      <x:c r="F11" s="14" t="d">
+        <x:v>2026-09-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G11" s="7" t="str">
         <x:v>男学生修复源说明与导出交叉检查记录</x:v>
@@ -632,8 +638,8 @@
       <x:c r="E12" s="7" t="str">
         <x:v>9 月 29 日材质验收有效；White 最新衣裤材质以 CA-001 的 9 月 30 日换装结果为准。</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="n">
-        <x:v>46294</x:v>
+      <x:c r="F12" s="14" t="d">
+        <x:v>2026-09-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G12" s="7" t="str">
         <x:v>学生布料参数、远处织纹与近景验收</x:v>
@@ -656,8 +662,8 @@
       <x:c r="E13" s="7" t="str">
         <x:v>本次图集保护已实现；后续图集或 UV 改动需更新遮罩。常驻纹理带来的内存增加按现有记录保留。</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="n">
-        <x:v>46294</x:v>
+      <x:c r="F13" s="14" t="d">
+        <x:v>2026-09-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G13" s="7" t="str">
         <x:v>男学生织物遮罩与图集采样设置</x:v>
@@ -680,8 +686,8 @@
       <x:c r="E14" s="7" t="str">
         <x:v>教学楼 B 修改后复查真实游戏画面及墙面、走廊显示。</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="n">
-        <x:v>46291</x:v>
+      <x:c r="F14" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G14" s="7" t="str">
         <x:v>教学楼 B 修复记录：真实 PIE 回切验证</x:v>
@@ -704,8 +710,8 @@
       <x:c r="E15" s="7" t="str">
         <x:v>本项视觉通过不覆盖真实角色通行；相关运行验收依后续证据更新。</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="n">
-        <x:v>46288</x:v>
+      <x:c r="F15" s="14" t="d">
+        <x:v>2026-09-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G15" s="7" t="str">
         <x:v>校医室材质与视觉完成记录</x:v>
@@ -728,8 +734,8 @@
       <x:c r="E16" s="7" t="str">
         <x:v>后续面部外观修改以同一正侧面检查为准；身体与颈部保留现有材质。</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="n">
-        <x:v>46291</x:v>
+      <x:c r="F16" s="14" t="d">
+        <x:v>2026-09-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G16" s="7" t="str">
         <x:v>Purple 面部问题定位、着色修复与保存检查</x:v>
@@ -752,8 +758,8 @@
       <x:c r="E17" s="7" t="str">
         <x:v>当前覆盖编辑器画面与材质接入，未新增运行时渲染验收依据。</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F17" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G17" s="7" t="str">
         <x:v>景观草坪材质修正进展与最终截图</x:v>
@@ -776,8 +782,8 @@
       <x:c r="E18" s="7" t="str">
         <x:v>通过MPC_CampusWind调整风力；当前范围为校园可见植被。</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F18" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G18" s="7" t="str">
         <x:v>植被风动最终交付与完成说明</x:v>
@@ -800,8 +806,8 @@
       <x:c r="E19" s="7" t="str">
         <x:v>原网格采用低幅程序风，不能称为逐叶物理模拟。</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F19" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G19" s="7" t="str">
         <x:v>树冠和固定材质槽交付记录</x:v>
@@ -824,8 +830,8 @@
       <x:c r="E20" s="7" t="str">
         <x:v>花篮共享木质材质内藤茎保持固定，叶片仅低幅摆动。</x:v>
       </x:c>
-      <x:c r="F20" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F20" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G20" s="7" t="str">
         <x:v>特殊植被固定端与动态预览交付</x:v>
@@ -848,8 +854,8 @@
       <x:c r="E21" s="7" t="str">
         <x:v>设置已交付；转镜头仍发糊另见CA-049.02。</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="n">
-        <x:v>46298</x:v>
+      <x:c r="F21" s="14" t="d">
+        <x:v>2026-10-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G21" s="7" t="str">
         <x:v>配置与PIE补查</x:v>
@@ -872,8 +878,8 @@
       <x:c r="E22" s="7" t="str">
         <x:v>自发光效果的实际渲染成本不由零新增灯光数量推定。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F22" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G22" s="7" t="str">
         <x:v>长廊最终结果与昼夜材质说明</x:v>
@@ -896,8 +902,8 @@
       <x:c r="E23" s="7" t="str">
         <x:v>风动整体GPU成本基线仍见CA-043.06。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F23" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G23" s="7" t="str">
         <x:v>palms_verification风动检查</x:v>
@@ -920,8 +926,8 @@
       <x:c r="E24" s="7" t="str">
         <x:v>当前天空以CA-063和CA-064的后续结果为准，保留初版阶段记录。</x:v>
       </x:c>
-      <x:c r="F24" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F24" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G24" s="7" t="str">
         <x:v>夜景各轮保存与用户补月光</x:v>
@@ -944,8 +950,8 @@
       <x:c r="E25" s="7" t="str">
         <x:v>后续整体参考氛围以CA-063为准。</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F25" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G25" s="7" t="str">
         <x:v>NightSkyline verified</x:v>
@@ -968,8 +974,8 @@
       <x:c r="E26" s="7" t="str">
         <x:v>材质动效纳入昼夜控制，白天禁灯见CA-064.03。</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F26" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G26" s="7" t="str">
         <x:v>NightLandmarkFX verified</x:v>
@@ -992,8 +998,8 @@
       <x:c r="E27" s="7" t="str">
         <x:v>实际动效和保存通过；低开销预览与显存限制见CA-064.09。</x:v>
       </x:c>
-      <x:c r="F27" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F27" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G27" s="7" t="str">
         <x:v>最新左右扫荡聊天与保存回读</x:v>
@@ -1016,8 +1022,8 @@
       <x:c r="E28" s="7" t="str">
         <x:v>具体参考细节接受范围另见CA-063.06。</x:v>
       </x:c>
-      <x:c r="F28" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F28" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G28" s="7" t="str">
         <x:v>NightReference final_verified</x:v>
@@ -1040,8 +1046,8 @@
       <x:c r="E29" s="7" t="str">
         <x:v>当前发光随昼夜控制，白天保持关闭。</x:v>
       </x:c>
-      <x:c r="F29" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F29" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G29" s="7" t="str">
         <x:v>NightReference运行与保存</x:v>
@@ -1064,8 +1070,8 @@
       <x:c r="E30" s="7" t="str">
         <x:v>参数交付与参考效果细节接受分开，见CA-063.06。</x:v>
       </x:c>
-      <x:c r="F30" s="14" t="n">
-        <x:v>46299</x:v>
+      <x:c r="F30" s="14" t="d">
+        <x:v>2026-10-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G30" s="7" t="str">
         <x:v>final_verified水面设置</x:v>
@@ -1088,8 +1094,8 @@
       <x:c r="E31" s="7" t="str">
         <x:v>旧白天归零范围仍作为阶段历史；黄昏从17:00提前渐亮。</x:v>
       </x:c>
-      <x:c r="F31" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F31" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G31" s="7" t="str">
         <x:v>emissive_batching与最新使用说明</x:v>
@@ -1112,8 +1118,8 @@
       <x:c r="E32" s="7" t="str">
         <x:v>本项只判断白天后期层接入与权重；黑天空后续修复见CA-067.03。</x:v>
       </x:c>
-      <x:c r="F32" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F32" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G32" s="7" t="str">
         <x:v>独立白天后期交付及最新权重回读</x:v>
@@ -1136,8 +1142,8 @@
       <x:c r="E33" s="7" t="str">
         <x:v>太阳18:00落下；灯具17:00提前渐亮，月亮轨道见CA-068。</x:v>
       </x:c>
-      <x:c r="F33" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F33" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G33" s="7" t="str">
         <x:v>白天最终交付与使用说明</x:v>
@@ -1160,8 +1166,8 @@
       <x:c r="E34" s="7" t="str">
         <x:v>灯具启动与达到全亮分开判断；窗口和速度见CA-064.02、CA-064.04。</x:v>
       </x:c>
-      <x:c r="F34" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F34" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G34" s="7" t="str">
         <x:v>黄昏预览与发光材质回读</x:v>
@@ -1184,8 +1190,8 @@
       <x:c r="E35" s="7" t="str">
         <x:v>后续日出黑天空修复独立见CA-067.03。</x:v>
       </x:c>
-      <x:c r="F35" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F35" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G35" s="7" t="str">
         <x:v>正午云层修复交付与场景回读</x:v>
@@ -1208,8 +1214,8 @@
       <x:c r="E36" s="7" t="str">
         <x:v>这是照明参数与观感阶段交付，整体性能另见CA-064.09。</x:v>
       </x:c>
-      <x:c r="F36" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F36" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G36" s="7" t="str">
         <x:v>正午用户反馈及Lumen设置回读</x:v>
@@ -1232,8 +1238,8 @@
       <x:c r="E37" s="7" t="str">
         <x:v>原问题已有新修复依据，不继续固定为未解决。</x:v>
       </x:c>
-      <x:c r="F37" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F37" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G37" s="7" t="str">
         <x:v>黑天空根因、两轮运行及重载验证</x:v>
@@ -1256,8 +1262,8 @@
       <x:c r="E38" s="7" t="str">
         <x:v>后续门扇按用户改纯色，见CA-070.03；桌椅木纹保留。</x:v>
       </x:c>
-      <x:c r="F38" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F38" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G38" s="7" t="str">
         <x:v>教学楼真实材质保存与近景交付</x:v>
@@ -1280,8 +1286,8 @@
       <x:c r="E39" s="7" t="str">
         <x:v>此前木门贴图阶段已被纯色修订替代；开关不受此材质改动影响。</x:v>
       </x:c>
-      <x:c r="F39" s="14" t="n">
-        <x:v>46300</x:v>
+      <x:c r="F39" s="14" t="d">
+        <x:v>2026-10-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G39" s="7" t="str">
         <x:v>用户纯色纠正与918组件验证</x:v>
@@ -1304,8 +1310,8 @@
       <x:c r="E40" s="7" t="str">
         <x:v>不把修正前异常保留为当前失败；旋转全量检查见CA-071.05。</x:v>
       </x:c>
-      <x:c r="F40" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F40" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G40" s="7" t="str">
         <x:v>最新材质与近景检查</x:v>
@@ -1328,32 +1334,32 @@
       <x:c r="E41" s="7" t="str">
         <x:v>只覆盖已绑定室外铺装，不能扩大到所有校园材质。</x:v>
       </x:c>
-      <x:c r="F41" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F41" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G41" s="7" t="str">
         <x:v>65材质重载与昼夜干湿检查</x:v>
       </x:c>
       <x:c r="H41" s="16" t="str"/>
     </x:row>
-    <x:row r="42" ht="75" customHeight="1">
+    <x:row r="42" ht="92" customHeight="1">
       <x:c r="A42" s="7" t="str">
         <x:v>CA-073.04</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
-        <x:v>阴雨云层光照及正午曝光修正</x:v>
+        <x:v>晴雨云层光照及正午曝光修正</x:v>
       </x:c>
       <x:c r="C42" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D42" s="7" t="str">
-        <x:v>天气联动体积云、日照、天空光和雾；正午雨景偏暗已修正，天气曝光补偿不累加，昼夜降雨预览通过，夜间白天后期层权重仍为0。</x:v>
+        <x:v>天气光照曝光接入的旧阶段通过；10月8日追加动态雨云和雨天灯光，用户指出晴空丢失后已恢复晴朗白天及原夜空，四昼夜晴雨组合验证通过。</x:v>
       </x:c>
       <x:c r="E42" s="7" t="str">
-        <x:v>该项为天气效果接入；基础昼夜与原夜景基准保留阶段依据。</x:v>
-      </x:c>
-      <x:c r="F42" s="14" t="n">
-        <x:v>46301</x:v>
+        <x:v>动态雨云见CA-075，晴空恢复见CA-075.07；严格雨景还原仍见CA-075.06。</x:v>
+      </x:c>
+      <x:c r="F42" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G42" s="7" t="str">
         <x:v>最终天气重载及昼夜运行验证</x:v>
@@ -1376,53 +1382,317 @@
       <x:c r="E43" s="7" t="str">
         <x:v>最新雨量按加大版判断，不再沿用初版1800条配置。</x:v>
       </x:c>
-      <x:c r="F43" s="14" t="n">
-        <x:v>46301</x:v>
+      <x:c r="F43" s="14" t="d">
+        <x:v>2026-10-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G43" s="7" t="str">
         <x:v>加大雨量直接纠正与最终预览</x:v>
       </x:c>
       <x:c r="H43" s="16" t="str"/>
     </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="1"/>
-      <x:c r="B44" s="1"/>
-      <x:c r="C44" s="1"/>
-      <x:c r="D44" s="1"/>
-      <x:c r="E44" s="1"/>
-      <x:c r="F44" s="1"/>
-      <x:c r="G44" s="1"/>
-      <x:c r="H44" s="1"/>
-    </x:row>
-    <x:row r="45" ht="34" customHeight="1">
-      <x:c r="A45" s="3" t="str">
+    <x:row r="44" ht="75" customHeight="1">
+      <x:c r="A44" s="7" t="str">
+        <x:v>CA-074.03</x:v>
+      </x:c>
+      <x:c r="B44" s="7" t="str">
+        <x:v>受控灯具发光材质与实体灯接入</x:v>
+      </x:c>
+      <x:c r="C44" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D44" s="7" t="str">
+        <x:v>受控灯具的发光材质接入SwitchPower，现有16个局部灯引用进入回路；161回路的材质与灯光开关检查通过，疏散指示牌保持独立。</x:v>
+      </x:c>
+      <x:c r="E44" s="7" t="str">
+        <x:v>雨景后续新增食堂32盏暖灯另见CA-075.03。</x:v>
+      </x:c>
+      <x:c r="F44" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G44" s="7" t="str">
+        <x:v>场景材质绑定与回路运行检查</x:v>
+      </x:c>
+      <x:c r="H44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="75" customHeight="1">
+      <x:c r="A45" s="7" t="str">
+        <x:v>CA-075</x:v>
+      </x:c>
+      <x:c r="B45" s="7" t="str">
+        <x:v>雨天双层动态乌云与形变</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D45" s="7" t="str">
+        <x:v>按用户纠正加入两层不同速度的乌云移动与持续形变，天空材质保存。晴天恢复原天空的后续纠正见CA-075.07。</x:v>
+      </x:c>
+      <x:c r="E45" s="7" t="str">
+        <x:v>动态验证见CA-075.05；雨景严格一比一另见CA-075.06。</x:v>
+      </x:c>
+      <x:c r="F45" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G45" s="7" t="str">
+        <x:v>用户动态云层要求与最终保存交付</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="75" customHeight="1">
+      <x:c r="A46" s="7" t="str">
+        <x:v>CA-075.02</x:v>
+      </x:c>
+      <x:c r="B46" s="7" t="str">
+        <x:v>雨景积水反射与动态涟漪</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D46" s="7" t="str">
+        <x:v>6个天气地面母材质通过编译保存，保留原法线与纹理，湿度为0返回干地输入；积水反射、动态涟漪与雨滴实时画面已交付。</x:v>
+      </x:c>
+      <x:c r="E46" s="7" t="str">
+        <x:v>10月9日食堂广场新材质替换后的晴雨回归见CA-076.11，旧6母材质通过不覆盖新绑定。</x:v>
+      </x:c>
+      <x:c r="F46" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G46" s="7" t="str">
+        <x:v>wet_surface passed=true与雨景最终实拍</x:v>
+      </x:c>
+      <x:c r="H46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="92" customHeight="1">
+      <x:c r="A47" s="7" t="str">
+        <x:v>CA-075.07</x:v>
+      </x:c>
+      <x:c r="B47" s="7" t="str">
+        <x:v>晴朗白天天空与原版晴夜恢复</x:v>
+      </x:c>
+      <x:c r="C47" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D47" s="7" t="str">
+        <x:v>用户指出晴朗天空消失后，将非雨天气改为晴天，晴时CloudCoverage/WeatherBlend/RainAmount归零。原星空与月亮节点哈希保持，切回夜晚的亮度残留已修复，scene保存。</x:v>
+      </x:c>
+      <x:c r="E47" s="7" t="str">
+        <x:v>原版夜空作为晴朗夜晚标准；雨天才覆盖动态雨云。该恢复不关闭旧夜景细节差异CA-063.06。</x:v>
+      </x:c>
+      <x:c r="F47" s="14" t="d">
+        <x:v>2026-10-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G47" s="7" t="str">
+        <x:v>用户直接纠正、原天空哈希与saved=true</x:v>
+      </x:c>
+      <x:c r="H47" s="16" t="str"/>
+    </x:row>
+    <x:row r="48" ht="92" customHeight="1">
+      <x:c r="A48" s="7" t="str">
+        <x:v>CA-076</x:v>
+      </x:c>
+      <x:c r="B48" s="7" t="str">
+        <x:v>食堂广场石材铺装与分带纹理</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D48" s="7" t="str">
+        <x:v>生成石材Albedo并接入世界坐标法线、粗糙度及板块色差。最终石板96cm、缝0.4cm，深灰带周期640cm/宽34cm，覆盖旧80cm初版参数并保存。</x:v>
+      </x:c>
+      <x:c r="E48" s="7" t="str">
+        <x:v>严格参考图验收见CA-076.10；天气回归见CA-076.11。</x:v>
+      </x:c>
+      <x:c r="F48" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G48" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H48" s="16" t="str"/>
+    </x:row>
+    <x:row r="49" ht="58" customHeight="1">
+      <x:c r="A49" s="7" t="str">
+        <x:v>CA-076.02</x:v>
+      </x:c>
+      <x:c r="B49" s="7" t="str">
+        <x:v>食堂花坛与石质收边材质</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D49" s="7" t="str">
+        <x:v>更新花坛颗粒与风化石材，最终82处PlanterStone绑定已保存，最终实拍检查通过。</x:v>
+      </x:c>
+      <x:c r="E49" s="7" t="str">
+        <x:v>仅确认本次材质交付，整体还原范围见CA-076.10。</x:v>
+      </x:c>
+      <x:c r="F49" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G49" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="58" customHeight="1">
+      <x:c r="A50" s="7" t="str">
+        <x:v>CA-076.03</x:v>
+      </x:c>
+      <x:c r="B50" s="7" t="str">
+        <x:v>食堂广场木长椅材质</x:v>
+      </x:c>
+      <x:c r="C50" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D50" s="7" t="str">
+        <x:v>更新木长椅表面，最终110处OiledTimber绑定保存，成片外观检查通过。</x:v>
+      </x:c>
+      <x:c r="E50" s="7" t="str">
+        <x:v>不以材质交付替代长椅坐下或角色通行回归。</x:v>
+      </x:c>
+      <x:c r="F50" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G50" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="58" customHeight="1">
+      <x:c r="A51" s="7" t="str">
+        <x:v>CA-076.04</x:v>
+      </x:c>
+      <x:c r="B51" s="7" t="str">
+        <x:v>食堂浅石立面材质</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D51" s="7" t="str">
+        <x:v>食堂立面浅石质感调整并保存，最终522处FacadeStone绑定，最终实拍确认。</x:v>
+      </x:c>
+      <x:c r="E51" s="7" t="str">
+        <x:v>建筑内部细节仍有参考差异，见CA-076.10。</x:v>
+      </x:c>
+      <x:c r="F51" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G51" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="75" customHeight="1">
+      <x:c r="A52" s="7" t="str">
+        <x:v>CA-076.05</x:v>
+      </x:c>
+      <x:c r="B52" s="7" t="str">
+        <x:v>食堂玻璃材质调整</x:v>
+      </x:c>
+      <x:c r="C52" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D52" s="7" t="str">
+        <x:v>修正过透明的玻璃表现，84处CanteenGlass绑定保存；最终答复仍明确玻璃反射与照片有差异。</x:v>
+      </x:c>
+      <x:c r="E52" s="7" t="str">
+        <x:v>本项为材质实现，反射一比一接受范围见CA-076.10。</x:v>
+      </x:c>
+      <x:c r="F52" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G52" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H52" s="16" t="str"/>
+    </x:row>
+    <x:row r="53" ht="58" customHeight="1">
+      <x:c r="A53" s="7" t="str">
+        <x:v>CA-076.06</x:v>
+      </x:c>
+      <x:c r="B53" s="7" t="str">
+        <x:v>榕树叶色与风动保持</x:v>
+      </x:c>
+      <x:c r="C53" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D53" s="7" t="str">
+        <x:v>降低榕树过饱和叶色，2处BanyanLeaves材质绑定保存，源说明确认保留原风动。</x:v>
+      </x:c>
+      <x:c r="E53" s="7" t="str">
+        <x:v>不扩大为全部树木风动重新验收；树冠叶片形态差异见CA-076.10。</x:v>
+      </x:c>
+      <x:c r="F53" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G53" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H53" s="16" t="str"/>
+    </x:row>
+    <x:row r="54" ht="75" customHeight="1">
+      <x:c r="A54" s="7" t="str">
+        <x:v>CA-076.08</x:v>
+      </x:c>
+      <x:c r="B54" s="7" t="str">
+        <x:v>食堂参考机位日照与云层调整</x:v>
+      </x:c>
+      <x:c r="C54" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D54" s="7" t="str">
+        <x:v>调整太阳方位80度、天空补光2.4与体积云布局，最终10:30晴天参考相机CR09_ReferenceCamera实拍核对并保存。</x:v>
+      </x:c>
+      <x:c r="E54" s="7" t="str">
+        <x:v>日照画面为晴天固定机位；完整昼夜晴雨恢复见CA-076.11。</x:v>
+      </x:c>
+      <x:c r="F54" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G54" s="7" t="str">
+        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="34" customHeight="1">
+      <x:c r="A56" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B45" s="21" t="str">
+      <x:c r="B56" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C45" s="21"/>
-      <x:c r="D45" s="21"/>
-      <x:c r="E45" s="21"/>
-      <x:c r="F45" s="21"/>
-      <x:c r="G45" s="21"/>
-      <x:c r="H45" s="21"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="1"/>
-      <x:c r="B46" s="1"/>
-      <x:c r="C46" s="1"/>
-      <x:c r="D46" s="1"/>
-      <x:c r="E46" s="1"/>
-      <x:c r="F46" s="1"/>
-      <x:c r="G46" s="1"/>
-      <x:c r="H46" s="1"/>
+      <x:c r="C56" s="21"/>
+      <x:c r="D56" s="21"/>
+      <x:c r="E56" s="21"/>
+      <x:c r="F56" s="21"/>
+      <x:c r="G56" s="21"/>
+      <x:c r="H56" s="21"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B45:H45"/>
+    <x:mergeCell ref="B56:H56"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C43">
+  <x:conditionalFormatting sqref="C8:C54">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1434,13 +1704,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C43">
+    <x:dataValidation type="list" sqref="C8:C54">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ea651e963ac486d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc91c4a8baed4b2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ProjectProgress/表格/分类进展/材质渲染.xlsx
+++ b/ProjectProgress/表格/分类进展/材质渲染.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R6facfb6396e645b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材质渲染" sheetId="1" r:id="R5af24a04285741e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,8 +198,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A7:H54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CategoryProgress3" displayName="CategoryProgress3" ref="A7:H60" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A7:H60"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="编号"/>
     <x:tableColumn id="2" name="事项"/>
@@ -433,7 +433,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>更新于 2026-10-09 09:07:22（北京时间）</x:v>
+        <x:v>更新于 2026-10-10 09:11:56（北京时间）</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -470,22 +470,22 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="B5" s="5" t="n">
-        <x:f>COUNTIF(C8:C54,A5)</x:f>
-        <x:v>45</x:v>
+        <x:f>COUNTIF(C8:C60,A5)</x:f>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="1"/>
       <x:c r="D5" s="1" t="str">
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="E5" s="5" t="n">
-        <x:f>COUNTIF(C8:C54,D5)</x:f>
+        <x:f>COUNTIF(C8:C60,D5)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="1" t="str">
         <x:v>待确认</x:v>
       </x:c>
       <x:c r="G5" s="5" t="n">
-        <x:f>COUNTIF(C8:C54,F5)</x:f>
+        <x:f>COUNTIF(C8:C60,F5)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="H5" s="1"/>
@@ -1390,27 +1390,27 @@
       </x:c>
       <x:c r="H43" s="16" t="str"/>
     </x:row>
-    <x:row r="44" ht="75" customHeight="1">
+    <x:row r="44" ht="92" customHeight="1">
       <x:c r="A44" s="7" t="str">
         <x:v>CA-074.03</x:v>
       </x:c>
       <x:c r="B44" s="7" t="str">
-        <x:v>受控灯具发光材质与实体灯接入</x:v>
+        <x:v>受控灯具发光材质开关一致性</x:v>
       </x:c>
       <x:c r="C44" s="20" t="str">
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D44" s="7" t="str">
-        <x:v>受控灯具的发光材质接入SwitchPower，现有16个局部灯引用进入回路；161回路的材质与灯光开关检查通过，疏散指示牌保持独立。</x:v>
+        <x:v>原SwitchPower发光接入保留。10月9日修复后，全部161回路发光和实体照明状态核对通过；15个代表点真实E输入30次发光边沿验证通过。后续24教室新吊灯材质见CA-080.04。</x:v>
       </x:c>
       <x:c r="E44" s="7" t="str">
-        <x:v>雨景后续新增食堂32盏暖灯另见CA-075.03。</x:v>
+        <x:v>发光面切换与实际照亮分别判断；实体灯补齐见CA-074.08，最新教室材质和亮度验收见CA-080。</x:v>
       </x:c>
       <x:c r="F44" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G44" s="7" t="str">
-        <x:v>场景材质绑定与回路运行检查</x:v>
+        <x:v>runtime_circuits与30次发光边沿验证</x:v>
       </x:c>
       <x:c r="H44" s="16" t="str"/>
     </x:row>
@@ -1452,10 +1452,10 @@
         <x:v>6个天气地面母材质通过编译保存，保留原法线与纹理，湿度为0返回干地输入；积水反射、动态涟漪与雨滴实时画面已交付。</x:v>
       </x:c>
       <x:c r="E46" s="7" t="str">
-        <x:v>10月9日食堂广场新材质替换后的晴雨回归见CA-076.11，旧6母材质通过不覆盖新绑定。</x:v>
+        <x:v>原6天气母材质交付保留；全场新铺装雨湿和渐干现已通过CA-078.03，夜景往返另见CA-076.11。</x:v>
       </x:c>
       <x:c r="F46" s="14" t="d">
-        <x:v>2026-10-08T00:00:00.000Z</x:v>
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G46" s="7" t="str">
         <x:v>wet_surface passed=true与雨景最终实拍</x:v>
@@ -1486,7 +1486,7 @@
       </x:c>
       <x:c r="H47" s="16" t="str"/>
     </x:row>
-    <x:row r="48" ht="92" customHeight="1">
+    <x:row r="48" ht="109" customHeight="1">
       <x:c r="A48" s="7" t="str">
         <x:v>CA-076</x:v>
       </x:c>
@@ -1497,16 +1497,16 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="D48" s="7" t="str">
-        <x:v>生成石材Albedo并接入世界坐标法线、粗糙度及板块色差。最终石板96cm、缝0.4cm，深灰带周期640cm/宽34cm，覆盖旧80cm初版参数并保存。</x:v>
+        <x:v>食堂局部96cm石板及640cm深灰带阶段已保存；用户随后指出其他位置旧石板未替换，10月9日全面替换同类室外铺装并恢复原天气Shader。当前全场范围见CA-078，原局部参数仅保留阶段依据。</x:v>
       </x:c>
       <x:c r="E48" s="7" t="str">
-        <x:v>严格参考图验收见CA-076.10；天气回归见CA-076.11。</x:v>
+        <x:v>当前铺装以全场统一及实体砖缝变体为准；严格照片还原CA-076.10和夜景往返CA-076.11分别判断。</x:v>
       </x:c>
       <x:c r="F48" s="14" t="d">
         <x:v>2026-10-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="G48" s="7" t="str">
-        <x:v>最终DELIVERY、保存校验与聊天交付</x:v>
+        <x:v>原局部保存与全面替换最新用户纠正</x:v>
       </x:c>
       <x:c r="H48" s="16" t="str"/>
     </x:row>
@@ -1654,45 +1654,189 @@
       </x:c>
       <x:c r="H54" s="16" t="str"/>
     </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="1"/>
-      <x:c r="B55" s="1"/>
-      <x:c r="C55" s="1"/>
-      <x:c r="D55" s="1"/>
-      <x:c r="E55" s="1"/>
-      <x:c r="F55" s="1"/>
-      <x:c r="G55" s="1"/>
-      <x:c r="H55" s="1"/>
-    </x:row>
-    <x:row r="56" ht="34" customHeight="1">
-      <x:c r="A56" s="3" t="str">
+    <x:row r="55" ht="92" customHeight="1">
+      <x:c r="A55" s="7" t="str">
+        <x:v>CA-078</x:v>
+      </x:c>
+      <x:c r="B55" s="7" t="str">
+        <x:v>同类室外旧石板全场替换</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D55" s="7" t="str">
+        <x:v>按用户指出局部覆盖不足，全面匹配同类室外旧花岗岩铺装。最终1036处新材质绑定、1033处运行时可见，旧目标材质残留0；71网格默认槽验证，5910处无关槽保持。</x:v>
+      </x:c>
+      <x:c r="E55" s="7" t="str">
+        <x:v>范围为同类旧石板；初始1127槽包含源对象及批次，不计作独立地砖。食堂旧局部阶段CA-076保留历史。</x:v>
+      </x:c>
+      <x:c r="F55" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G55" s="7" t="str">
+        <x:v>用户全面替换纠正与最终保存核对</x:v>
+      </x:c>
+      <x:c r="H55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="92" customHeight="1">
+      <x:c r="A56" s="7" t="str">
+        <x:v>CA-078.02</x:v>
+      </x:c>
+      <x:c r="B56" s="7" t="str">
+        <x:v>新铺装完整湿润积水涟漪Shader</x:v>
+      </x:c>
+      <x:c r="C56" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D56" s="7" t="str">
+        <x:v>保留原天气控制器及参数集合，积水遮罩、湿色、粗糙度、雨滴涟漪和法线混合五段着色代码逐段一致。30秒过渡、18秒湿润、90秒干燥参数保持并保存。</x:v>
+      </x:c>
+      <x:c r="E56" s="7" t="str">
+        <x:v>运行渐干验收见CA-078.03；全昼夜版本范围见CA-076.11。</x:v>
+      </x:c>
+      <x:c r="F56" s="14" t="d">
+        <x:v>2026-10-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G56" s="7" t="str">
+        <x:v>weather_qa五段一致与保存确认</x:v>
+      </x:c>
+      <x:c r="H56" s="16" t="str"/>
+    </x:row>
+    <x:row r="57" ht="75" customHeight="1">
+      <x:c r="A57" s="7" t="str">
+        <x:v>CA-080.03</x:v>
+      </x:c>
+      <x:c r="B57" s="7" t="str">
+        <x:v>教室水磨石与灰绿墙裙材质</x:v>
+      </x:c>
+      <x:c r="C57" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D57" s="7" t="str">
+        <x:v>24教室统一水磨石地面及灰绿墙裙，调整颗粒尺度与共享表面法线，最终实时视口和场景保存核对通过。</x:v>
+      </x:c>
+      <x:c r="E57" s="7" t="str">
+        <x:v>实时截图仍可见光照噪点；严格参考验收见CA-080.11。</x:v>
+      </x:c>
+      <x:c r="F57" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G57" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H57" s="16" t="str"/>
+    </x:row>
+    <x:row r="58" ht="75" customHeight="1">
+      <x:c r="A58" s="7" t="str">
+        <x:v>CA-080.04</x:v>
+      </x:c>
+      <x:c r="B58" s="7" t="str">
+        <x:v>教室木色窗帘及吊灯材质修正</x:v>
+      </x:c>
+      <x:c r="C58" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D58" s="7" t="str">
+        <x:v>椅背黑斑定位为过强木纹法线，独立平滑木质着色保留木纹颜色；窗帘、墙裙和金属边框统一修正异常明暗，吊灯发光与回路同步。</x:v>
+      </x:c>
+      <x:c r="E58" s="7" t="str">
+        <x:v>只记录当前共享材质修正；不推断所有视角的光照噪点已消失。</x:v>
+      </x:c>
+      <x:c r="F58" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G58" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H58" s="16" t="str"/>
+    </x:row>
+    <x:row r="59" ht="92" customHeight="1">
+      <x:c r="A59" s="7" t="str">
+        <x:v>CA-080.05</x:v>
+      </x:c>
+      <x:c r="B59" s="7" t="str">
+        <x:v>教室底层顶棚补光与灯光基准</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D59" s="7" t="str">
+        <x:v>保持24间共432灯、每间18灯，不新增灯数量；384主照明+48柔和顶棚补光，最终保存强度18/36及间接强度1.8，纠正预览恢复遗漏隐藏灯光。</x:v>
+      </x:c>
+      <x:c r="E59" s="7" t="str">
+        <x:v>中途22.5/间接4为试调记录，已被最终balance_saved替代；昼夜开关验证见CA-080.09。</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G59" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="75" customHeight="1">
+      <x:c r="A60" s="7" t="str">
+        <x:v>CA-080.06</x:v>
+      </x:c>
+      <x:c r="B60" s="7" t="str">
+        <x:v>教室公告栏黑板标语文字镜像修正</x:v>
+      </x:c>
+      <x:c r="C60" s="20" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D60" s="7" t="str">
+        <x:v>共享图文平面UV横向修正并重新导入，144个组件使用正缩放；引擎UV0和重新载入后文字方向、受光与可读性确认通过。</x:v>
+      </x:c>
+      <x:c r="E60" s="7" t="str">
+        <x:v>曾在查询贴图通道时断言退出，最终重新载入修正并保存，不以中途导入成功代替最终显示。</x:v>
+      </x:c>
+      <x:c r="F60" s="14" t="d">
+        <x:v>2026-10-10T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G60" s="7" t="str">
+        <x:v>最新室内最终保存与专项验证</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="34" customHeight="1">
+      <x:c r="A62" s="3" t="str">
         <x:v>记录范围</x:v>
       </x:c>
-      <x:c r="B56" s="21" t="str">
+      <x:c r="B62" s="21" t="str">
         <x:v>状态以项目聊天及验收记录为依据，每条仅计入一个分类。缺少最终验收或需要决定的事项标为待确认。</x:v>
       </x:c>
-      <x:c r="C56" s="21"/>
-      <x:c r="D56" s="21"/>
-      <x:c r="E56" s="21"/>
-      <x:c r="F56" s="21"/>
-      <x:c r="G56" s="21"/>
-      <x:c r="H56" s="21"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="1"/>
-      <x:c r="B57" s="1"/>
-      <x:c r="C57" s="1"/>
-      <x:c r="D57" s="1"/>
-      <x:c r="E57" s="1"/>
-      <x:c r="F57" s="1"/>
-      <x:c r="G57" s="1"/>
-      <x:c r="H57" s="1"/>
+      <x:c r="C62" s="21"/>
+      <x:c r="D62" s="21"/>
+      <x:c r="E62" s="21"/>
+      <x:c r="F62" s="21"/>
+      <x:c r="G62" s="21"/>
+      <x:c r="H62" s="21"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="B56:H56"/>
+    <x:mergeCell ref="B62:H62"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="C8:C54">
+  <x:conditionalFormatting sqref="C8:C60">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>$C8="已完成"</x:formula>
     </x:cfRule>
@@ -1704,13 +1848,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="C8:C54">
+    <x:dataValidation type="list" sqref="C8:C60">
       <x:formula1>"已完成,进行中,待确认"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc91c4a8baed4b2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R402638700fee48a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>